--- a/hypersim9buses/Lineas_9bus_IEEE_hypersim.xlsx
+++ b/hypersim9buses/Lineas_9bus_IEEE_hypersim.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francesca\miniconda3\envs\gridcal_original2\datagen\hypersim9buses\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francesca\miniconda3\envs\hp2c-dt\datagen\hypersim9buses\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4940AE1-40E0-405E-988A-B3B5B5D8C853}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B844B19-ECDC-4FE1-B423-EEE5B8FCCF07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11496" windowHeight="4548" xr2:uid="{1208F1AD-02D5-4AAB-BFFC-88F9F8DC21CD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1208F1AD-02D5-4AAB-BFFC-88F9F8DC21CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,18 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -895,6 +907,22 @@
         <v>0.20899999999989427</v>
       </c>
     </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0">
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+    </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="P12" s="5"/>
     </row>
